--- a/public/fixtures/edge_geo.xlsx
+++ b/public/fixtures/edge_geo.xlsx
@@ -54211,7 +54211,7 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>12009</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">

--- a/public/fixtures/edge_geo.xlsx
+++ b/public/fixtures/edge_geo.xlsx
@@ -53931,7 +53931,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>09/05/1994</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -53972,7 +53972,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>05/11/2018</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54000,12 +54000,12 @@
       <c r="R18" s="14" t="n"/>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$33.70</t>
+          <t>$32.36</t>
         </is>
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>$50.55</t>
+          <t>$48.54</t>
         </is>
       </c>
       <c r="U18" s="11" t="inlineStr">
@@ -54041,12 +54041,12 @@
       <c r="AA18" s="11" t="n"/>
       <c r="AB18" s="11" t="inlineStr">
         <is>
-          <t>$32.74</t>
+          <t>$31.44</t>
         </is>
       </c>
       <c r="AC18" s="11" t="inlineStr">
         <is>
-          <t>$49.11</t>
+          <t>$47.16</t>
         </is>
       </c>
       <c r="AD18" s="11" t="inlineStr">
@@ -54066,18 +54066,18 @@
       </c>
       <c r="AG18" s="11" t="inlineStr">
         <is>
-          <t>$70,800.00</t>
+          <t>$68,100.00</t>
         </is>
       </c>
       <c r="AH18" s="11" t="n"/>
       <c r="AI18" s="11" t="inlineStr">
         <is>
-          <t>$31.78</t>
+          <t>$30.53</t>
         </is>
       </c>
       <c r="AJ18" s="11" t="inlineStr">
         <is>
-          <t>$47.67</t>
+          <t>$45.80</t>
         </is>
       </c>
       <c r="AK18" s="11" t="inlineStr">
@@ -54097,18 +54097,18 @@
       </c>
       <c r="AN18" s="11" t="inlineStr">
         <is>
-          <t>$68,700.00</t>
+          <t>$66,100.00</t>
         </is>
       </c>
       <c r="AO18" s="11" t="n"/>
       <c r="AP18" s="11" t="inlineStr">
         <is>
-          <t>$30.87</t>
+          <t>$29.62</t>
         </is>
       </c>
       <c r="AQ18" s="11" t="inlineStr">
         <is>
-          <t>$46.30</t>
+          <t>$44.43</t>
         </is>
       </c>
       <c r="AR18" s="11" t="inlineStr">
@@ -54128,7 +54128,7 @@
       </c>
       <c r="AU18" s="11" t="inlineStr">
         <is>
-          <t>$66,800.00</t>
+          <t>$64,200.00</t>
         </is>
       </c>
       <c r="AV18" s="11" t="inlineStr">
@@ -54196,12 +54196,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>08/28/1993</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54241,7 +54241,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>08/19/2014</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54269,12 +54269,12 @@
       <c r="R19" s="14" t="n"/>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$16.78</t>
+          <t>$16.11</t>
         </is>
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>$25.17</t>
+          <t>$24.16</t>
         </is>
       </c>
       <c r="U19" s="11" t="inlineStr">
@@ -54310,12 +54310,12 @@
       <c r="AA19" s="11" t="n"/>
       <c r="AB19" s="11" t="inlineStr">
         <is>
-          <t>$16.30</t>
+          <t>$15.62</t>
         </is>
       </c>
       <c r="AC19" s="11" t="inlineStr">
         <is>
-          <t>$24.45</t>
+          <t>$23.43</t>
         </is>
       </c>
       <c r="AD19" s="11" t="inlineStr">
@@ -54335,18 +54335,18 @@
       </c>
       <c r="AG19" s="11" t="inlineStr">
         <is>
-          <t>$35,300.00</t>
+          <t>$33,900.00</t>
         </is>
       </c>
       <c r="AH19" s="11" t="n"/>
       <c r="AI19" s="11" t="inlineStr">
         <is>
-          <t>$15.82</t>
+          <t>$15.19</t>
         </is>
       </c>
       <c r="AJ19" s="11" t="inlineStr">
         <is>
-          <t>$23.73</t>
+          <t>$22.79</t>
         </is>
       </c>
       <c r="AK19" s="11" t="inlineStr">
@@ -54366,18 +54366,18 @@
       </c>
       <c r="AN19" s="11" t="inlineStr">
         <is>
-          <t>$34,200.00</t>
+          <t>$32,900.00</t>
         </is>
       </c>
       <c r="AO19" s="11" t="n"/>
       <c r="AP19" s="11" t="inlineStr">
         <is>
-          <t>$15.34</t>
+          <t>$14.71</t>
         </is>
       </c>
       <c r="AQ19" s="11" t="inlineStr">
         <is>
-          <t>$23.01</t>
+          <t>$22.07</t>
         </is>
       </c>
       <c r="AR19" s="11" t="inlineStr">
@@ -54397,7 +54397,7 @@
       </c>
       <c r="AU19" s="11" t="inlineStr">
         <is>
-          <t>$33,200.00</t>
+          <t>$31,900.00</t>
         </is>
       </c>
       <c r="AV19" s="11" t="inlineStr">
@@ -54465,12 +54465,12 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>10/10/1963</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -54510,7 +54510,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>02/04/2023</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54538,12 +54538,12 @@
       <c r="R20" s="14" t="n"/>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$18.70</t>
+          <t>$17.93</t>
         </is>
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>$28.05</t>
+          <t>$26.89</t>
         </is>
       </c>
       <c r="U20" s="11" t="inlineStr">
@@ -54579,12 +54579,12 @@
       <c r="AA20" s="11" t="n"/>
       <c r="AB20" s="11" t="inlineStr">
         <is>
-          <t>$18.17</t>
+          <t>$17.45</t>
         </is>
       </c>
       <c r="AC20" s="11" t="inlineStr">
         <is>
-          <t>$27.26</t>
+          <t>$26.17</t>
         </is>
       </c>
       <c r="AD20" s="11" t="inlineStr">
@@ -54604,18 +54604,18 @@
       </c>
       <c r="AG20" s="11" t="inlineStr">
         <is>
-          <t>$39,300.00</t>
+          <t>$37,800.00</t>
         </is>
       </c>
       <c r="AH20" s="11" t="n"/>
       <c r="AI20" s="11" t="inlineStr">
         <is>
-          <t>$17.64</t>
+          <t>$16.92</t>
         </is>
       </c>
       <c r="AJ20" s="11" t="inlineStr">
         <is>
-          <t>$26.46</t>
+          <t>$25.38</t>
         </is>
       </c>
       <c r="AK20" s="11" t="inlineStr">
@@ -54635,18 +54635,18 @@
       </c>
       <c r="AN20" s="11" t="inlineStr">
         <is>
-          <t>$38,200.00</t>
+          <t>$36,700.00</t>
         </is>
       </c>
       <c r="AO20" s="11" t="n"/>
       <c r="AP20" s="11" t="inlineStr">
         <is>
-          <t>$17.12</t>
+          <t>$16.44</t>
         </is>
       </c>
       <c r="AQ20" s="11" t="inlineStr">
         <is>
-          <t>$25.68</t>
+          <t>$24.66</t>
         </is>
       </c>
       <c r="AR20" s="11" t="inlineStr">
@@ -54666,7 +54666,7 @@
       </c>
       <c r="AU20" s="11" t="inlineStr">
         <is>
-          <t>$37,000.00</t>
+          <t>$35,600.00</t>
         </is>
       </c>
       <c r="AV20" s="11" t="inlineStr">

--- a/public/fixtures/edge_geo.xlsx
+++ b/public/fixtures/edge_geo.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priority Census Template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Census Definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROVENANCE" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
@@ -33,6 +33,7 @@
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId26"/>
   </externalReferences>
   <definedNames>
     <definedName name="_____dc1" hidden="1">{#N/A,#N/A,FALSE,"COVER PAGE";#N/A,#N/A,FALSE,"HIGHLITES";#N/A,#N/A,FALSE,"INC STATE (1)";#N/A,#N/A,FALSE,"DPC BY DEPT";#N/A,#N/A,FALSE,"FIXED COSTS";#N/A,#N/A,FALSE,"PRODUCTION";#N/A,#N/A,FALSE,"SALES TRND";#N/A,#N/A,FALSE,"BALANCE SHEET";#N/A,#N/A,FALSE,"INVENTORY";#N/A,#N/A,FALSE,"MFG VAR";#N/A,#N/A,FALSE,"OVRHD SPND";#N/A,#N/A,FALSE,"ENERGY COSTS";#N/A,#N/A,FALSE,"MAINTENANCE";#N/A,#N/A,FALSE,"LABOR";#N/A,#N/A,FALSE,"ACTVSFORECAST"}</definedName>
@@ -53931,7 +53932,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>09/05/1994</t>
+          <t>09/09/1966</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -53972,7 +53973,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>05/11/2018</t>
+          <t>02/03/2021</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54196,7 +54197,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>08/28/1993</t>
+          <t>02/02/1963</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -54241,7 +54242,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>08/19/2014</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54465,12 +54466,12 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>10/10/1963</t>
+          <t>01/13/1966</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -54510,7 +54511,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>02/04/2023</t>
+          <t>02/05/2021</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -62293,4 +62294,471 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nine Dean — simulated census: data provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>generated 2026-07-20 00:01 from the reference warehouse (public.ext_*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>warehouse table</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>vintage</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MIT · Living Wage Calculator</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ext_mit_expense</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>301,824</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>mit:livingwage.mit.edu:2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Engine A basket components</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MIT · Living Wage Calculator</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ext_mit_living_wage</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>113,184</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>mit:livingwage.mit.edu:2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Engine A living-wage reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EPI · Family Budget Calculator</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ext_epi_cost</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>502,880</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>epi:2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Engine A basket (food, childcare, medical, housing, other)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EPI · Family Budget Calculator</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ext_epi_county</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3,143</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>epi:2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Engine A county coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ACS · B25064 median gross rent</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ext_acs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3,222</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>acs:5y2023-B25064</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Engine A housing candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CNT · H+T Affordability Index</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ext_cnt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3,144</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>cnt:2022</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Engine A transportation (override, not MAX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BLS OEWS · state wages</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ext_bls_oews_state_wage</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>35,427</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>May2024</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>wages by state+SOC (p10/p25/median); prevailing-wage overlay</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>O*NET · SOC occupations</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ext_onet_soc_occupation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1,016</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>O*NET 29.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>job titles and SOC codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>O*NET · SOC alternate titles</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ext_onet_soc_alt_title</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>55,119</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>O*NET 29.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>title → SOC matching</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Census · ZCTA↔county crosswalk</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ext_census_zcta_county</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>23,355</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>census_zcta:2020</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>residence ZIP → county</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Census · county gazetteer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ext_census_county</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3,222</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>census_county:2024</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>county names / states</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A Better Balance · PSL statutes</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ext_abb_psl_law</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>abb:2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Engine B floors (cap / preempted / no-cap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KFF · EHBS benchmarks</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ext_kff_ehbs_health_benchmarks</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>kff_ehbs:2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Engine C employer-contribution thresholds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Peterson-KFF · OOP cost-sharing</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ext_peterson_kff_oop_costsharing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>live scrape; page modified 2026-02-11</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Engine C out-of-pocket exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PolicyEngine US</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>in-process library (not a warehouse table)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>policyengine-us 1.745.0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Engine A federal + state + payroll + local tax</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/fixtures/edge_geo.xlsx
+++ b/public/fixtures/edge_geo.xlsx
@@ -53932,7 +53932,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>09/09/1966</t>
+          <t>11/07/1972</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -53973,7 +53973,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>02/03/2021</t>
+          <t>07/20/2017</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54197,12 +54197,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>02/02/1963</t>
+          <t>01/21/1986</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54242,7 +54242,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>11/04/2013</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54466,12 +54466,12 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>01/13/1966</t>
+          <t>02/14/1979</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -54511,7 +54511,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>02/05/2021</t>
+          <t>07/06/2019</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -62322,7 +62322,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 00:01 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 00:25 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/edge_geo.xlsx
+++ b/public/fixtures/edge_geo.xlsx
@@ -53932,12 +53932,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>11/07/1972</t>
+          <t>06/10/1999</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53973,7 +53973,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>07/20/2017</t>
+          <t>01/03/2018</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54197,7 +54197,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>01/21/1986</t>
+          <t>03/07/1972</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -54242,7 +54242,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>11/04/2013</t>
+          <t>12/16/2021</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54466,12 +54466,12 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>02/14/1979</t>
+          <t>11/07/1976</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -54511,7 +54511,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>07/06/2019</t>
+          <t>04/15/2012</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -62322,7 +62322,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 00:25 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 12:56 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/edge_geo.xlsx
+++ b/public/fixtures/edge_geo.xlsx
@@ -53075,7 +53075,11 @@
           <t>Company Name:</t>
         </is>
       </c>
-      <c r="B8" s="46" t="n"/>
+      <c r="B8" s="46" t="inlineStr">
+        <is>
+          <t>Three Rivers Facilities Services, Inc.</t>
+        </is>
+      </c>
       <c r="C8" s="46" t="n"/>
       <c r="D8" s="46" t="n"/>
       <c r="E8" s="45" t="n"/>
@@ -53140,7 +53144,11 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="B9" s="43" t="n"/>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>07/20/2026</t>
+        </is>
+      </c>
       <c r="C9" s="43" t="n"/>
       <c r="D9" s="43" t="n"/>
       <c r="E9" s="43" t="n"/>
@@ -53932,7 +53940,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>06/10/1999</t>
+          <t>12/16/1969</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -53973,7 +53981,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>01/03/2018</t>
+          <t>11/05/2014</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54197,7 +54205,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>03/07/1972</t>
+          <t>01/17/1970</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -54242,7 +54250,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>12/16/2021</t>
+          <t>09/27/2022</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54466,7 +54474,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>11/07/1976</t>
+          <t>03/23/1980</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -54511,7 +54519,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>04/15/2012</t>
+          <t>02/17/2025</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -62322,7 +62330,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 12:56 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 18:20 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/edge_geo.xlsx
+++ b/public/fixtures/edge_geo.xlsx
@@ -53940,7 +53940,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>12/16/1969</t>
+          <t>08/04/1981</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -53961,7 +53961,7 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>15-2021</t>
+          <t>39-4031</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -53971,7 +53971,7 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>Mathematicians</t>
+          <t>Morticians, Undertakers, and Funeral Arrangers</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
@@ -53981,7 +53981,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>11/05/2014</t>
+          <t>07/12/2012</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54009,12 +54009,12 @@
       <c r="R18" s="14" t="n"/>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$32.36</t>
+          <t>$13.03</t>
         </is>
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>$48.54</t>
+          <t>$19.54</t>
         </is>
       </c>
       <c r="U18" s="11" t="inlineStr">
@@ -54034,7 +54034,7 @@
       </c>
       <c r="X18" s="11" t="inlineStr">
         <is>
-          <t>$2,800.00</t>
+          <t>$1,100.00</t>
         </is>
       </c>
       <c r="Y18" s="11" t="inlineStr">
@@ -54044,18 +54044,18 @@
       </c>
       <c r="Z18" s="11" t="inlineStr">
         <is>
-          <t>$70,100.00</t>
+          <t>$28,200.00</t>
         </is>
       </c>
       <c r="AA18" s="11" t="n"/>
       <c r="AB18" s="11" t="inlineStr">
         <is>
-          <t>$31.44</t>
+          <t>$12.64</t>
         </is>
       </c>
       <c r="AC18" s="11" t="inlineStr">
         <is>
-          <t>$47.16</t>
+          <t>$18.96</t>
         </is>
       </c>
       <c r="AD18" s="11" t="inlineStr">
@@ -54065,7 +54065,7 @@
       </c>
       <c r="AE18" s="11" t="inlineStr">
         <is>
-          <t>$2,700.00</t>
+          <t>$1,100.00</t>
         </is>
       </c>
       <c r="AF18" s="11" t="inlineStr">
@@ -54075,18 +54075,18 @@
       </c>
       <c r="AG18" s="11" t="inlineStr">
         <is>
-          <t>$68,100.00</t>
+          <t>$27,400.00</t>
         </is>
       </c>
       <c r="AH18" s="11" t="n"/>
       <c r="AI18" s="11" t="inlineStr">
         <is>
-          <t>$30.53</t>
+          <t>$12.26</t>
         </is>
       </c>
       <c r="AJ18" s="11" t="inlineStr">
         <is>
-          <t>$45.80</t>
+          <t>$18.39</t>
         </is>
       </c>
       <c r="AK18" s="11" t="inlineStr">
@@ -54096,7 +54096,7 @@
       </c>
       <c r="AL18" s="11" t="inlineStr">
         <is>
-          <t>$2,600.00</t>
+          <t>$1,100.00</t>
         </is>
       </c>
       <c r="AM18" s="11" t="inlineStr">
@@ -54106,18 +54106,18 @@
       </c>
       <c r="AN18" s="11" t="inlineStr">
         <is>
-          <t>$66,100.00</t>
+          <t>$26,600.00</t>
         </is>
       </c>
       <c r="AO18" s="11" t="n"/>
       <c r="AP18" s="11" t="inlineStr">
         <is>
-          <t>$29.62</t>
+          <t>$11.92</t>
         </is>
       </c>
       <c r="AQ18" s="11" t="inlineStr">
         <is>
-          <t>$44.43</t>
+          <t>$17.88</t>
         </is>
       </c>
       <c r="AR18" s="11" t="inlineStr">
@@ -54127,7 +54127,7 @@
       </c>
       <c r="AS18" s="11" t="inlineStr">
         <is>
-          <t>$2,600.00</t>
+          <t>$1,000.00</t>
         </is>
       </c>
       <c r="AT18" s="11" t="inlineStr">
@@ -54137,7 +54137,7 @@
       </c>
       <c r="AU18" s="11" t="inlineStr">
         <is>
-          <t>$64,200.00</t>
+          <t>$25,800.00</t>
         </is>
       </c>
       <c r="AV18" s="11" t="inlineStr">
@@ -54205,7 +54205,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>01/17/1970</t>
+          <t>11/19/2000</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -54230,7 +54230,7 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>39-3092</t>
+          <t>11-9081</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
@@ -54240,7 +54240,7 @@
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>Costume Attendants</t>
+          <t>Lodging Managers</t>
         </is>
       </c>
       <c r="J19" s="14" t="inlineStr">
@@ -54250,7 +54250,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>09/27/2022</t>
+          <t>06/12/2024</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54278,12 +54278,12 @@
       <c r="R19" s="14" t="n"/>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$16.11</t>
+          <t>$15.82</t>
         </is>
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>$24.16</t>
+          <t>$23.73</t>
         </is>
       </c>
       <c r="U19" s="11" t="inlineStr">
@@ -54313,18 +54313,18 @@
       </c>
       <c r="Z19" s="11" t="inlineStr">
         <is>
-          <t>$34,900.00</t>
+          <t>$34,300.00</t>
         </is>
       </c>
       <c r="AA19" s="11" t="n"/>
       <c r="AB19" s="11" t="inlineStr">
         <is>
-          <t>$15.62</t>
+          <t>$15.38</t>
         </is>
       </c>
       <c r="AC19" s="11" t="inlineStr">
         <is>
-          <t>$23.43</t>
+          <t>$23.07</t>
         </is>
       </c>
       <c r="AD19" s="11" t="inlineStr">
@@ -54334,7 +54334,7 @@
       </c>
       <c r="AE19" s="11" t="inlineStr">
         <is>
-          <t>$1,400.00</t>
+          <t>$1,300.00</t>
         </is>
       </c>
       <c r="AF19" s="11" t="inlineStr">
@@ -54344,18 +54344,18 @@
       </c>
       <c r="AG19" s="11" t="inlineStr">
         <is>
-          <t>$33,900.00</t>
+          <t>$33,300.00</t>
         </is>
       </c>
       <c r="AH19" s="11" t="n"/>
       <c r="AI19" s="11" t="inlineStr">
         <is>
-          <t>$15.19</t>
+          <t>$14.90</t>
         </is>
       </c>
       <c r="AJ19" s="11" t="inlineStr">
         <is>
-          <t>$22.79</t>
+          <t>$22.35</t>
         </is>
       </c>
       <c r="AK19" s="11" t="inlineStr">
@@ -54375,18 +54375,18 @@
       </c>
       <c r="AN19" s="11" t="inlineStr">
         <is>
-          <t>$32,900.00</t>
+          <t>$32,300.00</t>
         </is>
       </c>
       <c r="AO19" s="11" t="n"/>
       <c r="AP19" s="11" t="inlineStr">
         <is>
-          <t>$14.71</t>
+          <t>$14.47</t>
         </is>
       </c>
       <c r="AQ19" s="11" t="inlineStr">
         <is>
-          <t>$22.07</t>
+          <t>$21.71</t>
         </is>
       </c>
       <c r="AR19" s="11" t="inlineStr">
@@ -54406,7 +54406,7 @@
       </c>
       <c r="AU19" s="11" t="inlineStr">
         <is>
-          <t>$31,900.00</t>
+          <t>$31,400.00</t>
         </is>
       </c>
       <c r="AV19" s="11" t="inlineStr">
@@ -54474,12 +54474,12 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>03/23/1980</t>
+          <t>08/08/1997</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -54499,7 +54499,7 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>11-9081</t>
+          <t>43-5061</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
@@ -54509,7 +54509,7 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>Lodging Managers</t>
+          <t>Production, Planning, and Expediting Clerks</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
@@ -54519,7 +54519,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>02/17/2025</t>
+          <t>01/24/2022</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54547,12 +54547,12 @@
       <c r="R20" s="14" t="n"/>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$17.93</t>
+          <t>$15.82</t>
         </is>
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>$26.89</t>
+          <t>$23.73</t>
         </is>
       </c>
       <c r="U20" s="11" t="inlineStr">
@@ -54572,7 +54572,7 @@
       </c>
       <c r="X20" s="11" t="inlineStr">
         <is>
-          <t>$1,600.00</t>
+          <t>$1,400.00</t>
         </is>
       </c>
       <c r="Y20" s="11" t="inlineStr">
@@ -54582,18 +54582,18 @@
       </c>
       <c r="Z20" s="11" t="inlineStr">
         <is>
-          <t>$38,900.00</t>
+          <t>$34,300.00</t>
         </is>
       </c>
       <c r="AA20" s="11" t="n"/>
       <c r="AB20" s="11" t="inlineStr">
         <is>
-          <t>$17.45</t>
+          <t>$15.38</t>
         </is>
       </c>
       <c r="AC20" s="11" t="inlineStr">
         <is>
-          <t>$26.17</t>
+          <t>$23.07</t>
         </is>
       </c>
       <c r="AD20" s="11" t="inlineStr">
@@ -54603,7 +54603,7 @@
       </c>
       <c r="AE20" s="11" t="inlineStr">
         <is>
-          <t>$1,500.00</t>
+          <t>$1,300.00</t>
         </is>
       </c>
       <c r="AF20" s="11" t="inlineStr">
@@ -54613,18 +54613,18 @@
       </c>
       <c r="AG20" s="11" t="inlineStr">
         <is>
-          <t>$37,800.00</t>
+          <t>$33,300.00</t>
         </is>
       </c>
       <c r="AH20" s="11" t="n"/>
       <c r="AI20" s="11" t="inlineStr">
         <is>
-          <t>$16.92</t>
+          <t>$14.90</t>
         </is>
       </c>
       <c r="AJ20" s="11" t="inlineStr">
         <is>
-          <t>$25.38</t>
+          <t>$22.35</t>
         </is>
       </c>
       <c r="AK20" s="11" t="inlineStr">
@@ -54634,7 +54634,7 @@
       </c>
       <c r="AL20" s="11" t="inlineStr">
         <is>
-          <t>$1,500.00</t>
+          <t>$1,300.00</t>
         </is>
       </c>
       <c r="AM20" s="11" t="inlineStr">
@@ -54644,18 +54644,18 @@
       </c>
       <c r="AN20" s="11" t="inlineStr">
         <is>
-          <t>$36,700.00</t>
+          <t>$32,300.00</t>
         </is>
       </c>
       <c r="AO20" s="11" t="n"/>
       <c r="AP20" s="11" t="inlineStr">
         <is>
-          <t>$16.44</t>
+          <t>$14.47</t>
         </is>
       </c>
       <c r="AQ20" s="11" t="inlineStr">
         <is>
-          <t>$24.66</t>
+          <t>$21.71</t>
         </is>
       </c>
       <c r="AR20" s="11" t="inlineStr">
@@ -54665,7 +54665,7 @@
       </c>
       <c r="AS20" s="11" t="inlineStr">
         <is>
-          <t>$1,400.00</t>
+          <t>$1,300.00</t>
         </is>
       </c>
       <c r="AT20" s="11" t="inlineStr">
@@ -54675,7 +54675,7 @@
       </c>
       <c r="AU20" s="11" t="inlineStr">
         <is>
-          <t>$35,600.00</t>
+          <t>$31,400.00</t>
         </is>
       </c>
       <c r="AV20" s="11" t="inlineStr">
@@ -62330,7 +62330,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 18:20 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 19:46 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/edge_geo.xlsx
+++ b/public/fixtures/edge_geo.xlsx
@@ -53146,7 +53146,7 @@
       </c>
       <c r="B9" s="43" t="inlineStr">
         <is>
-          <t>07/20/2026</t>
+          <t>07/21/2026</t>
         </is>
       </c>
       <c r="C9" s="43" t="n"/>
@@ -53940,12 +53940,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>08/04/1981</t>
+          <t>11/19/2000</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53961,7 +53961,7 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>39-4031</t>
+          <t>51-9195</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -53971,7 +53971,7 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>Morticians, Undertakers, and Funeral Arrangers</t>
+          <t>Glass Blowers, Molders, Benders, and Finishers</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
@@ -53981,7 +53981,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>07/12/2012</t>
+          <t>09/06/2020</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54009,12 +54009,12 @@
       <c r="R18" s="14" t="n"/>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$13.03</t>
+          <t>$13.32</t>
         </is>
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>$19.54</t>
+          <t>$19.98</t>
         </is>
       </c>
       <c r="U18" s="11" t="inlineStr">
@@ -54034,7 +54034,7 @@
       </c>
       <c r="X18" s="11" t="inlineStr">
         <is>
-          <t>$1,100.00</t>
+          <t>$1,200.00</t>
         </is>
       </c>
       <c r="Y18" s="11" t="inlineStr">
@@ -54044,18 +54044,18 @@
       </c>
       <c r="Z18" s="11" t="inlineStr">
         <is>
-          <t>$28,200.00</t>
+          <t>$28,900.00</t>
         </is>
       </c>
       <c r="AA18" s="11" t="n"/>
       <c r="AB18" s="11" t="inlineStr">
         <is>
-          <t>$12.64</t>
+          <t>$12.98</t>
         </is>
       </c>
       <c r="AC18" s="11" t="inlineStr">
         <is>
-          <t>$18.96</t>
+          <t>$19.47</t>
         </is>
       </c>
       <c r="AD18" s="11" t="inlineStr">
@@ -54075,18 +54075,18 @@
       </c>
       <c r="AG18" s="11" t="inlineStr">
         <is>
-          <t>$27,400.00</t>
+          <t>$28,100.00</t>
         </is>
       </c>
       <c r="AH18" s="11" t="n"/>
       <c r="AI18" s="11" t="inlineStr">
         <is>
-          <t>$12.26</t>
+          <t>$12.60</t>
         </is>
       </c>
       <c r="AJ18" s="11" t="inlineStr">
         <is>
-          <t>$18.39</t>
+          <t>$18.90</t>
         </is>
       </c>
       <c r="AK18" s="11" t="inlineStr">
@@ -54106,18 +54106,18 @@
       </c>
       <c r="AN18" s="11" t="inlineStr">
         <is>
-          <t>$26,600.00</t>
+          <t>$27,300.00</t>
         </is>
       </c>
       <c r="AO18" s="11" t="n"/>
       <c r="AP18" s="11" t="inlineStr">
         <is>
-          <t>$11.92</t>
+          <t>$12.21</t>
         </is>
       </c>
       <c r="AQ18" s="11" t="inlineStr">
         <is>
-          <t>$17.88</t>
+          <t>$18.32</t>
         </is>
       </c>
       <c r="AR18" s="11" t="inlineStr">
@@ -54127,7 +54127,7 @@
       </c>
       <c r="AS18" s="11" t="inlineStr">
         <is>
-          <t>$1,000.00</t>
+          <t>$1,100.00</t>
         </is>
       </c>
       <c r="AT18" s="11" t="inlineStr">
@@ -54137,7 +54137,7 @@
       </c>
       <c r="AU18" s="11" t="inlineStr">
         <is>
-          <t>$25,800.00</t>
+          <t>$26,500.00</t>
         </is>
       </c>
       <c r="AV18" s="11" t="inlineStr">
@@ -54205,12 +54205,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>11/19/2000</t>
+          <t>08/12/1981</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54230,7 +54230,7 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>11-9081</t>
+          <t>29-2092</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
@@ -54240,7 +54240,7 @@
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>Lodging Managers</t>
+          <t>Hearing Aid Specialists</t>
         </is>
       </c>
       <c r="J19" s="14" t="inlineStr">
@@ -54250,7 +54250,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>06/12/2024</t>
+          <t>03/22/2018</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54278,12 +54278,12 @@
       <c r="R19" s="14" t="n"/>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$15.82</t>
+          <t>$16.39</t>
         </is>
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>$23.73</t>
+          <t>$24.59</t>
         </is>
       </c>
       <c r="U19" s="11" t="inlineStr">
@@ -54313,18 +54313,18 @@
       </c>
       <c r="Z19" s="11" t="inlineStr">
         <is>
-          <t>$34,300.00</t>
+          <t>$35,500.00</t>
         </is>
       </c>
       <c r="AA19" s="11" t="n"/>
       <c r="AB19" s="11" t="inlineStr">
         <is>
-          <t>$15.38</t>
+          <t>$15.91</t>
         </is>
       </c>
       <c r="AC19" s="11" t="inlineStr">
         <is>
-          <t>$23.07</t>
+          <t>$23.87</t>
         </is>
       </c>
       <c r="AD19" s="11" t="inlineStr">
@@ -54334,7 +54334,7 @@
       </c>
       <c r="AE19" s="11" t="inlineStr">
         <is>
-          <t>$1,300.00</t>
+          <t>$1,400.00</t>
         </is>
       </c>
       <c r="AF19" s="11" t="inlineStr">
@@ -54344,18 +54344,18 @@
       </c>
       <c r="AG19" s="11" t="inlineStr">
         <is>
-          <t>$33,300.00</t>
+          <t>$34,500.00</t>
         </is>
       </c>
       <c r="AH19" s="11" t="n"/>
       <c r="AI19" s="11" t="inlineStr">
         <is>
-          <t>$14.90</t>
+          <t>$15.48</t>
         </is>
       </c>
       <c r="AJ19" s="11" t="inlineStr">
         <is>
-          <t>$22.35</t>
+          <t>$23.22</t>
         </is>
       </c>
       <c r="AK19" s="11" t="inlineStr">
@@ -54375,18 +54375,18 @@
       </c>
       <c r="AN19" s="11" t="inlineStr">
         <is>
-          <t>$32,300.00</t>
+          <t>$33,500.00</t>
         </is>
       </c>
       <c r="AO19" s="11" t="n"/>
       <c r="AP19" s="11" t="inlineStr">
         <is>
-          <t>$14.47</t>
+          <t>$15.00</t>
         </is>
       </c>
       <c r="AQ19" s="11" t="inlineStr">
         <is>
-          <t>$21.71</t>
+          <t>$22.50</t>
         </is>
       </c>
       <c r="AR19" s="11" t="inlineStr">
@@ -54406,7 +54406,7 @@
       </c>
       <c r="AU19" s="11" t="inlineStr">
         <is>
-          <t>$31,400.00</t>
+          <t>$32,500.00</t>
         </is>
       </c>
       <c r="AV19" s="11" t="inlineStr">
@@ -54474,7 +54474,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>08/08/1997</t>
+          <t>08/04/1977</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -54499,7 +54499,7 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>43-5061</t>
+          <t>15-1299</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
@@ -54509,7 +54509,7 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>Production, Planning, and Expediting Clerks</t>
+          <t>Computer Occupations, All Other</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
@@ -54519,7 +54519,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>01/24/2022</t>
+          <t>07/16/2016</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54547,12 +54547,12 @@
       <c r="R20" s="14" t="n"/>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$15.82</t>
+          <t>$20.53</t>
         </is>
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>$23.73</t>
+          <t>$30.80</t>
         </is>
       </c>
       <c r="U20" s="11" t="inlineStr">
@@ -54572,7 +54572,7 @@
       </c>
       <c r="X20" s="11" t="inlineStr">
         <is>
-          <t>$1,400.00</t>
+          <t>$1,800.00</t>
         </is>
       </c>
       <c r="Y20" s="11" t="inlineStr">
@@ -54582,18 +54582,18 @@
       </c>
       <c r="Z20" s="11" t="inlineStr">
         <is>
-          <t>$34,300.00</t>
+          <t>$44,500.00</t>
         </is>
       </c>
       <c r="AA20" s="11" t="n"/>
       <c r="AB20" s="11" t="inlineStr">
         <is>
-          <t>$15.38</t>
+          <t>$19.95</t>
         </is>
       </c>
       <c r="AC20" s="11" t="inlineStr">
         <is>
-          <t>$23.07</t>
+          <t>$29.92</t>
         </is>
       </c>
       <c r="AD20" s="11" t="inlineStr">
@@ -54603,7 +54603,7 @@
       </c>
       <c r="AE20" s="11" t="inlineStr">
         <is>
-          <t>$1,300.00</t>
+          <t>$1,700.00</t>
         </is>
       </c>
       <c r="AF20" s="11" t="inlineStr">
@@ -54613,18 +54613,18 @@
       </c>
       <c r="AG20" s="11" t="inlineStr">
         <is>
-          <t>$33,300.00</t>
+          <t>$43,200.00</t>
         </is>
       </c>
       <c r="AH20" s="11" t="n"/>
       <c r="AI20" s="11" t="inlineStr">
         <is>
-          <t>$14.90</t>
+          <t>$19.33</t>
         </is>
       </c>
       <c r="AJ20" s="11" t="inlineStr">
         <is>
-          <t>$22.35</t>
+          <t>$28.99</t>
         </is>
       </c>
       <c r="AK20" s="11" t="inlineStr">
@@ -54634,7 +54634,7 @@
       </c>
       <c r="AL20" s="11" t="inlineStr">
         <is>
-          <t>$1,300.00</t>
+          <t>$1,700.00</t>
         </is>
       </c>
       <c r="AM20" s="11" t="inlineStr">
@@ -54644,18 +54644,18 @@
       </c>
       <c r="AN20" s="11" t="inlineStr">
         <is>
-          <t>$32,300.00</t>
+          <t>$41,900.00</t>
         </is>
       </c>
       <c r="AO20" s="11" t="n"/>
       <c r="AP20" s="11" t="inlineStr">
         <is>
-          <t>$14.47</t>
+          <t>$18.80</t>
         </is>
       </c>
       <c r="AQ20" s="11" t="inlineStr">
         <is>
-          <t>$21.71</t>
+          <t>$28.20</t>
         </is>
       </c>
       <c r="AR20" s="11" t="inlineStr">
@@ -54665,7 +54665,7 @@
       </c>
       <c r="AS20" s="11" t="inlineStr">
         <is>
-          <t>$1,300.00</t>
+          <t>$1,600.00</t>
         </is>
       </c>
       <c r="AT20" s="11" t="inlineStr">
@@ -54675,7 +54675,7 @@
       </c>
       <c r="AU20" s="11" t="inlineStr">
         <is>
-          <t>$31,400.00</t>
+          <t>$40,700.00</t>
         </is>
       </c>
       <c r="AV20" s="11" t="inlineStr">
@@ -62330,7 +62330,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 19:46 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-21 18:04 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/edge_geo.xlsx
+++ b/public/fixtures/edge_geo.xlsx
@@ -53146,7 +53146,7 @@
       </c>
       <c r="B9" s="43" t="inlineStr">
         <is>
-          <t>07/21/2026</t>
+          <t>07/22/2026</t>
         </is>
       </c>
       <c r="C9" s="43" t="n"/>
@@ -53940,12 +53940,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>11/19/2000</t>
+          <t>04/24/1981</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53981,7 +53981,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>09/06/2020</t>
+          <t>12/11/2019</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54205,12 +54205,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>08/12/1981</t>
+          <t>05/21/1970</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54250,7 +54250,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>03/22/2018</t>
+          <t>01/04/2025</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54474,7 +54474,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>08/04/1977</t>
+          <t>08/12/1977</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -54519,7 +54519,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>07/16/2016</t>
+          <t>12/18/2015</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -62330,7 +62330,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-21 18:04 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-22 14:39 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>
